--- a/49917_Intercuenca_49917/_raw_reportes_xlsx/IDConfig_8101_completo.xlsx
+++ b/49917_Intercuenca_49917/_raw_reportes_xlsx/IDConfig_8101_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R18be4734c58a4ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rddb163294c454a92"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,156 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    142.2470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    142.0320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.8020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.0150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.3320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.6210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.6360</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.4660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>13/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49917_Intercuenca_49917/_raw_reportes_xlsx/IDConfig_8101_completo.xlsx
+++ b/49917_Intercuenca_49917/_raw_reportes_xlsx/IDConfig_8101_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rddb163294c454a92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbeb84341e35744a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,666 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.8130</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.5350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.7950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.1050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.1950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.4190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.5730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.6250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.5730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.8660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.7370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.9290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    142.0020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.7670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.4170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.4120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.8130</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.8150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.3210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.1540</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.4150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.7470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.0410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.7950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.4880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.3920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.4340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    139.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.6180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.8850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.9760</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.1210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.5530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.8740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    142.0540</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
